--- a/feedback_forms/004_workplace_collaboration_quiz--feedback_forms.xlsx
+++ b/feedback_forms/004_workplace_collaboration_quiz--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>communication_channels_used</t>
+          <t>manager_support</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Communication Channels Used</t>
+          <t>Manager Support</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>manager_support</t>
+          <t>communication_channels_used</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Manager Support</t>
+          <t>Communication Channels Used</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>team_size</t>
+          <t>manager_support_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Team Size</t>
+          <t>Manager Support 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,320 +768,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>collaboration_level</t>
+          <t>team_dynamics_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Collaboration Level</t>
+          <t>Team Dynamics 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>conflict_resolution</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Conflict Resolution</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>communication_channels</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Communication Channels</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>work_flow</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Work Flow</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>collaboration_tools</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Collaboration Tools</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>team_dynamics</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Team Dynamics</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>communication_channels_used</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Communication Channels Used</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>manager_support</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Manager Support</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>team_size</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Team Size</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>collaboration_level</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Collaboration Level</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>conflict_resolution</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Conflict Resolution</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>communication_channels</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Communication Channels</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>work_flow</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Work Flow</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>collaboration_tools</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Collaboration Tools</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,7 +799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C71"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -1148,12 +849,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>formal</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Formal</t>
         </is>
       </c>
     </row>
@@ -1165,29 +866,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>formal</t>
+          <t>informal</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Formal</t>
+          <t>Informal</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>communication_style_choices</t>
+          <t>collaboration_level_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>informal</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Informal</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1199,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1216,46 +917,46 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>collaboration_level_choices</t>
+          <t>conflict_resolution_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>direct</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Direct</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>collaboration_level_choices</t>
+          <t>conflict_resolution_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>indirect</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Indirect</t>
         </is>
       </c>
     </row>
@@ -1267,46 +968,46 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>direct</t>
+          <t>mediation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Mediation</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>conflict_resolution_choices</t>
+          <t>communication_channels_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>indirect</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indirect</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>conflict_resolution_choices</t>
+          <t>communication_channels_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>mediation</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mediation</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1318,46 +1019,46 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>In-Person</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>communication_channels_choices</t>
+          <t>work_flow_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>agile</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Agile</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>communication_channels_choices</t>
+          <t>work_flow_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>in-person</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>In-Person</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
@@ -1369,46 +1070,46 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>agile</t>
+          <t>waterfall</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Agile</t>
+          <t>Waterfall</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>work_flow_choices</t>
+          <t>collaboration_tools_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hybrid</t>
+          <t>trello</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Trello</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>work_flow_choices</t>
+          <t>collaboration_tools_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>waterfall</t>
+          <t>asana</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Waterfall</t>
+          <t>Asana</t>
         </is>
       </c>
     </row>
@@ -1420,46 +1121,46 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>trello</t>
+          <t>jira</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Trello</t>
+          <t>Jira</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>collaboration_tools_choices</t>
+          <t>team_dynamics_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>asana</t>
+          <t>high-functioning</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Asana</t>
+          <t>High-Functioning</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>collaboration_tools_choices</t>
+          <t>team_dynamics_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>jira</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jira</t>
+          <t>Functional</t>
         </is>
       </c>
     </row>
@@ -1471,63 +1172,63 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>high-functioning</t>
+          <t>low-functioning</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>High-Functioning</t>
+          <t>Low-Functioning</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>team_dynamics_choices</t>
+          <t>manager_support_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>functional</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>team_dynamics_choices</t>
+          <t>manager_support_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>low-functioning</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Low-Functioning</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>communication_channels_used_choices</t>
+          <t>manager_support_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1240,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1556,760 +1257,131 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>video_conferencing</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Video Conferencing</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>manager_support_choices</t>
+          <t>communication_channels_used_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>video_conferencing</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Video Conferencing</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>manager_support_choices</t>
+          <t>manager_support_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>manager_support_choices</t>
+          <t>manager_support_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>collaboration_level_choices</t>
+          <t>manager_support_2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>collaboration_level_choices</t>
+          <t>team_dynamics_2_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>high-functioning</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>High-Functioning</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>collaboration_level_choices</t>
+          <t>team_dynamics_2_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>functional</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Functional</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>collaboration_level_choices</t>
+          <t>team_dynamics_2_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>low-functioning</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>conflict_resolution_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>conflict_resolution_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>indirect</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Indirect</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>conflict_resolution_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>mediation</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Mediation</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>communication_channels_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>communication_channels_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>communication_channels_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>in-person</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>In-Person</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>work_flow_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>agile</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Agile</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>work_flow_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>hybrid</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Hybrid</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>work_flow_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>waterfall</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Waterfall</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>collaboration_tools_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>trello</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Trello</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>collaboration_tools_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>asana</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Asana</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>collaboration_tools_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>jira</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Jira</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>team_dynamics_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>high-functioning</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>High-Functioning</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>team_dynamics_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>functional</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>team_dynamics_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>low-functioning</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
           <t>Low-Functioning</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>communication_channels_used_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>communication_channels_used_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>communication_channels_used_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>video_conferencing</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Video Conferencing</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>manager_support_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>manager_support_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>manager_support_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>collaboration_level_choices</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>collaboration_level_choices</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>collaboration_level_choices</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>collaboration_level_choices</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>conflict_resolution_choices</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>direct</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Direct</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>conflict_resolution_choices</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>indirect</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Indirect</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>conflict_resolution_choices</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>mediation</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Mediation</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>communication_channels_choices</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>communication_channels_choices</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>communication_channels_choices</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>in-person</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>In-Person</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>work_flow_choices</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>agile</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Agile</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>work_flow_choices</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>hybrid</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Hybrid</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>work_flow_choices</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>waterfall</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Waterfall</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>collaboration_tools_choices</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>trello</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Trello</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>collaboration_tools_choices</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>asana</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Asana</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>collaboration_tools_choices</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>jira</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Jira</t>
         </is>
       </c>
     </row>
